--- a/output/Test_Cases_collection/TC07 - Checkout with Empty First Name.xlsx
+++ b/output/Test_Cases_collection/TC07 - Checkout with Empty First Name.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="35">
   <si>
     <t>Test Case Name</t>
   </si>
@@ -64,70 +64,52 @@
     <t>7</t>
   </si>
   <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>Launch the application and open `https://www.saucedemo.com/`.</t>
-  </si>
-  <si>
-    <t>Enter `standard_user` in the "user-name" field.</t>
-  </si>
-  <si>
-    <t>Enter `secret_sauce` in the "password" field.</t>
-  </si>
-  <si>
-    <t>Click on "login-button".</t>
-  </si>
-  <si>
-    <t>Click on "add-to-cart-sauce-labs-backpack".</t>
-  </si>
-  <si>
-    <t>Click on "checkout".</t>
-  </si>
-  <si>
-    <t>Leave the "firstName" field empty.</t>
-  </si>
-  <si>
-    <t>Enter "test" in the "lastName" field.</t>
-  </si>
-  <si>
-    <t>Enter "67868766" in the "postalCode" field.</t>
-  </si>
-  <si>
-    <t>Click on "continue".</t>
-  </si>
-  <si>
-    <t>The login page is displayed with username and password fields.</t>
-  </si>
-  <si>
-    <t>The username is entered successfully.</t>
-  </si>
-  <si>
-    <t>The password is entered successfully.</t>
-  </si>
-  <si>
-    <t>The user is redirected to the inventory page.</t>
-  </si>
-  <si>
-    <t>The item is added to the cart, and the cart icon shows "1".</t>
-  </si>
-  <si>
-    <t>The user is redirected to the checkout step one page.</t>
-  </si>
-  <si>
-    <t>The first name field remains empty.</t>
-  </si>
-  <si>
-    <t>The last name is entered successfully.</t>
-  </si>
-  <si>
-    <t>The postal code is entered successfully.</t>
-  </si>
-  <si>
-    <t>An error message is displayed: "Error: First Name is required".</t>
+    <t>Launch the application and open [https://www.saucedemo.com/]</t>
+  </si>
+  <si>
+    <t>Log in with valid credentials ("standard_user" and "secret_sauce")</t>
+  </si>
+  <si>
+    <t>Add "Sauce Labs Backpack" to the cart</t>
+  </si>
+  <si>
+    <t>Click on "checkout"</t>
+  </si>
+  <si>
+    <t>Leave "firstName" field empty</t>
+  </si>
+  <si>
+    <t>Enter "test" in the "lastName" field</t>
+  </si>
+  <si>
+    <t>Enter "76565" in the "postalCode" field</t>
+  </si>
+  <si>
+    <t>Click on "continue"</t>
+  </si>
+  <si>
+    <t>Application is launched successfully</t>
+  </si>
+  <si>
+    <t>User is redirected to [https://www.saucedemo.com/inventory.html]</t>
+  </si>
+  <si>
+    <t>Item is added to the cart successfully</t>
+  </si>
+  <si>
+    <t>User is redirected to [https://www.saucedemo.com/checkout-step-one.html]</t>
+  </si>
+  <si>
+    <t>"firstName" field is empty</t>
+  </si>
+  <si>
+    <t>Last name is entered successfully</t>
+  </si>
+  <si>
+    <t>Postal code is entered successfully</t>
+  </si>
+  <si>
+    <t>Error message "Error: First Name is required" is displayed</t>
   </si>
   <si>
     <t>New</t>
@@ -494,7 +476,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -528,19 +510,19 @@
         <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="E2" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F2" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="G2" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -551,16 +533,16 @@
         <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E3" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F3" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -571,16 +553,16 @@
         <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F4" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -591,16 +573,16 @@
         <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D5" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="E5" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F5" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -611,16 +593,16 @@
         <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D6" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E6" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F6" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -631,16 +613,16 @@
         <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D7" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E7" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F7" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -651,16 +633,16 @@
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D8" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E8" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F8" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -671,56 +653,16 @@
         <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D9" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="E9" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F9" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" t="s">
-        <v>7</v>
-      </c>
-      <c r="B10" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" t="s">
-        <v>26</v>
-      </c>
-      <c r="D10" t="s">
-        <v>36</v>
-      </c>
-      <c r="E10" t="s">
-        <v>38</v>
-      </c>
-      <c r="F10" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B11" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" t="s">
-        <v>27</v>
-      </c>
-      <c r="D11" t="s">
-        <v>37</v>
-      </c>
-      <c r="E11" t="s">
-        <v>38</v>
-      </c>
-      <c r="F11" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
